--- a/data/trans_dic/P04D$individual-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,62; 47,53</t>
+          <t>36,99; 46,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,77; 39,41</t>
+          <t>30,32; 39,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,36; 30,34</t>
+          <t>22,3; 30,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,15; 49,91</t>
+          <t>38,36; 49,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,08; 48,66</t>
+          <t>37,71; 48,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,16; 28,21</t>
+          <t>20,95; 27,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,05; 46,72</t>
+          <t>39,4; 47,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,88; 42,15</t>
+          <t>35,37; 42,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,82; 28,03</t>
+          <t>22,55; 27,9</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,46; 45,49</t>
+          <t>35,26; 45,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,2; 37,96</t>
+          <t>28,46; 38,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,37; 28,51</t>
+          <t>19,06; 27,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,54; 40,97</t>
+          <t>29,07; 40,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,28; 43,61</t>
+          <t>33,39; 43,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,11; 27,42</t>
+          <t>20,71; 27,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,15; 41,6</t>
+          <t>33,99; 41,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,88; 39,49</t>
+          <t>31,93; 39,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,89; 26,92</t>
+          <t>20,97; 26,84</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,65; 34,13</t>
+          <t>26,76; 34,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,47; 34,76</t>
+          <t>26,18; 34,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,29; 79,95</t>
+          <t>17,01; 78,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,7; 34,14</t>
+          <t>22,82; 34,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,88; 41,63</t>
+          <t>26,85; 42,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,09; 20,56</t>
+          <t>11,36; 21,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,66; 32,84</t>
+          <t>26,52; 32,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,41; 34,78</t>
+          <t>27,36; 34,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 75,95</t>
+          <t>16,42; 77,69</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 26,84</t>
+          <t>21,65; 26,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,41; 31,08</t>
+          <t>25,71; 30,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 17,51</t>
+          <t>12,82; 17,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 32,7</t>
+          <t>25,71; 32,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 34,31</t>
+          <t>27,79; 34,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 18,33</t>
+          <t>6,51; 18,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,01; 28,14</t>
+          <t>23,9; 28,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,54; 31,65</t>
+          <t>27,51; 31,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 16,81</t>
+          <t>10,11; 16,76</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 22,64</t>
+          <t>15,75; 22,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,54; 23,68</t>
+          <t>16,61; 23,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 17,43</t>
+          <t>10,34; 17,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,24; 27,87</t>
+          <t>21,52; 27,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 24,68</t>
+          <t>18,25; 24,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 13,55</t>
+          <t>8,29; 13,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,85; 24,89</t>
+          <t>19,63; 24,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 22,84</t>
+          <t>18,36; 22,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,01</t>
+          <t>9,71; 13,96</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,91; 42,5</t>
+          <t>30,49; 42,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,61; 36,95</t>
+          <t>25,81; 36,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 29,22</t>
+          <t>9,87; 28,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,85; 27,08</t>
+          <t>21,95; 27,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,73; 33,28</t>
+          <t>27,73; 33,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,76; 15,74</t>
+          <t>10,67; 15,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,45; 28,95</t>
+          <t>24,35; 29,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,09; 33,22</t>
+          <t>28,15; 33,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,32; 17,2</t>
+          <t>11,16; 17,03</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,25; 31,25</t>
+          <t>28,09; 31,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,88; 30,13</t>
+          <t>27,14; 30,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,97; 41,85</t>
+          <t>17,8; 41,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,8; 29,87</t>
+          <t>26,87; 29,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,34; 32,57</t>
+          <t>29,33; 32,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,71; 17,12</t>
+          <t>12,49; 17,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,77; 30,21</t>
+          <t>27,76; 30,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,6; 30,9</t>
+          <t>28,73; 31,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,4; 30,08</t>
+          <t>16,39; 30,61</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>164479; 207803</t>
+          <t>161720; 205116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>127737; 169117</t>
+          <t>130108; 170999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112716; 152958</t>
+          <t>112426; 152625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119961; 156949</t>
+          <t>120636; 156010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>128701; 168892</t>
+          <t>130888; 168838</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94385; 125841</t>
+          <t>93458; 124775</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>293505; 351164</t>
+          <t>296191; 353466</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>270756; 327148</t>
+          <t>274485; 329456</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216869; 266371</t>
+          <t>214339; 265182</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>147642; 189430</t>
+          <t>146829; 189131</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106361; 143197</t>
+          <t>107370; 144068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87595; 128905</t>
+          <t>86191; 126009</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99853; 138472</t>
+          <t>98266; 136759</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>123880; 162335</t>
+          <t>124311; 163229</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76945; 104903</t>
+          <t>79242; 106133</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>257633; 313825</t>
+          <t>256400; 312826</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>238977; 295973</t>
+          <t>239322; 295415</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>174396; 224720</t>
+          <t>175034; 224073</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>167766; 214808</t>
+          <t>168438; 218442</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>138163; 181398</t>
+          <t>136627; 177677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115392; 533503</t>
+          <t>113518; 525836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59054; 88815</t>
+          <t>59367; 89983</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44653; 69154</t>
+          <t>44604; 70648</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18317; 33964</t>
+          <t>18772; 36030</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>237196; 292117</t>
+          <t>235921; 290811</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>188617; 239307</t>
+          <t>188216; 238732</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139367; 632261</t>
+          <t>136674; 646768</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>250730; 310544</t>
+          <t>250510; 307822</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>292158; 357312</t>
+          <t>295572; 355455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>129489; 180708</t>
+          <t>132231; 183173</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>198227; 250353</t>
+          <t>196871; 249025</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>230966; 283346</t>
+          <t>229538; 285031</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72639; 179062</t>
+          <t>63620; 179470</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>461711; 541081</t>
+          <t>459543; 539953</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>543989; 625186</t>
+          <t>543494; 625971</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>195689; 337640</t>
+          <t>203054; 336576</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81032; 115154</t>
+          <t>80119; 116755</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102639; 146960</t>
+          <t>103082; 143777</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48640; 82620</t>
+          <t>49032; 83646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>161508; 211942</t>
+          <t>163647; 210234</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>135498; 182219</t>
+          <t>134709; 180409</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67950; 113760</t>
+          <t>69627; 115978</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>251945; 315930</t>
+          <t>249090; 312345</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>246709; 310331</t>
+          <t>249461; 308868</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129011; 184055</t>
+          <t>127592; 183366</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>82236; 113050</t>
+          <t>81100; 113923</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73551; 106111</t>
+          <t>74111; 105256</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22411; 70277</t>
+          <t>23736; 67911</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>241944; 299850</t>
+          <t>243000; 301882</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>300003; 360047</t>
+          <t>300090; 361757</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81773; 119627</t>
+          <t>81075; 118732</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>335786; 397536</t>
+          <t>334381; 401047</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>384566; 454886</t>
+          <t>385446; 454363</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>113273; 172036</t>
+          <t>111681; 170391</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>964584; 1067163</t>
+          <t>959257; 1071189</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>910224; 1020006</t>
+          <t>918855; 1024531</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>605709; 1410439</t>
+          <t>599932; 1397069</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>950137; 1059144</t>
+          <t>952920; 1061610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1036191; 1150203</t>
+          <t>1035900; 1145841</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>453751; 611098</t>
+          <t>445836; 611692</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1932729; 2103039</t>
+          <t>1932517; 2098898</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1978580; 2137748</t>
+          <t>1987150; 2144320</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1138177; 2087390</t>
+          <t>1137263; 2124200</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$individual-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,99; 46,91</t>
+          <t>37,69; 47,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,32; 39,85</t>
+          <t>30,87; 40,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,3; 30,27</t>
+          <t>21,92; 29,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,36; 49,61</t>
+          <t>37,71; 49,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,71; 48,65</t>
+          <t>37,59; 48,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,95; 27,97</t>
+          <t>20,52; 27,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,4; 47,02</t>
+          <t>39,11; 46,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,37; 42,45</t>
+          <t>35,27; 42,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,55; 27,9</t>
+          <t>22,24; 27,32</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,26; 45,42</t>
+          <t>35,11; 45,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,46; 38,19</t>
+          <t>28,04; 38,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,06; 27,87</t>
+          <t>18,84; 27,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,07; 40,46</t>
+          <t>29,66; 40,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 43,85</t>
+          <t>33,41; 44,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 27,74</t>
+          <t>20,78; 27,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,99; 41,47</t>
+          <t>34,29; 41,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,93; 39,41</t>
+          <t>31,88; 39,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 26,84</t>
+          <t>20,34; 26,22</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,76; 34,71</t>
+          <t>26,6; 34,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,18; 34,04</t>
+          <t>25,79; 34,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 78,8</t>
+          <t>14,19; 21,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,82; 34,59</t>
+          <t>22,54; 34,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,85; 42,53</t>
+          <t>27,1; 42,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,36; 21,81</t>
+          <t>10,64; 20,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,52; 32,69</t>
+          <t>26,62; 32,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,36; 34,7</t>
+          <t>27,84; 35,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,42; 77,69</t>
+          <t>14,09; 20,08</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,65; 26,6</t>
+          <t>21,34; 26,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 30,92</t>
+          <t>25,5; 30,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,75</t>
+          <t>13,26; 18,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 32,52</t>
+          <t>25,64; 32,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,79; 34,51</t>
+          <t>27,82; 34,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 18,38</t>
+          <t>15,33; 19,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,9; 28,08</t>
+          <t>23,96; 28,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,51; 31,69</t>
+          <t>27,34; 31,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 16,76</t>
+          <t>14,74; 18,08</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,75; 22,95</t>
+          <t>15,61; 22,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,61; 23,16</t>
+          <t>16,56; 22,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 17,65</t>
+          <t>8,99; 15,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,52; 27,65</t>
+          <t>21,46; 27,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,25; 24,44</t>
+          <t>18,23; 24,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,82</t>
+          <t>10,31; 14,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,63; 24,61</t>
+          <t>19,99; 24,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,73</t>
+          <t>18,46; 22,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,96</t>
+          <t>10,44; 13,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,49; 42,83</t>
+          <t>31,06; 43,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,81; 36,66</t>
+          <t>25,89; 37,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 28,24</t>
+          <t>10,2; 27,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,95; 27,26</t>
+          <t>21,74; 26,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,73; 33,43</t>
+          <t>27,61; 33,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,63</t>
+          <t>10,29; 15,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,35; 29,2</t>
+          <t>24,25; 29,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,15; 33,19</t>
+          <t>28,13; 33,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,16; 17,03</t>
+          <t>10,99; 16,17</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,09; 31,37</t>
+          <t>28,05; 31,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,14; 30,26</t>
+          <t>27,05; 30,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,8; 41,46</t>
+          <t>16,5; 19,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,87; 29,94</t>
+          <t>26,78; 29,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,33; 32,45</t>
+          <t>29,32; 32,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,13</t>
+          <t>15,61; 17,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,76; 30,15</t>
+          <t>27,9; 30,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,73; 31,0</t>
+          <t>28,67; 30,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,39; 30,61</t>
+          <t>16,32; 18,22</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131122</t>
+          <t>140766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>108677</t>
+          <t>116530</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>239799</t>
+          <t>257296</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>161720; 205116</t>
+          <t>164796; 205718</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130108; 170999</t>
+          <t>132469; 172848</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112426; 152625</t>
+          <t>120450; 163799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120636; 156010</t>
+          <t>118569; 155975</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>130888; 168838</t>
+          <t>130465; 168166</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93458; 124775</t>
+          <t>99923; 132969</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>296191; 353466</t>
+          <t>293990; 352393</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>274485; 329456</t>
+          <t>273740; 327713</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>214339; 265182</t>
+          <t>230498; 283183</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>109423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91087</t>
+          <t>101796</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>196821</t>
+          <t>211219</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>146829; 189131</t>
+          <t>146194; 187913</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>107370; 144068</t>
+          <t>105756; 144736</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86191; 126009</t>
+          <t>91019; 131073</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98266; 136759</t>
+          <t>100255; 136321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>124311; 163229</t>
+          <t>124378; 164095</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79242; 106133</t>
+          <t>87929; 118275</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>256400; 312826</t>
+          <t>258682; 312723</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>239322; 295415</t>
+          <t>238909; 292425</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>175034; 224073</t>
+          <t>184361; 237605</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321696</t>
+          <t>82833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>346822</t>
+          <t>111318</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>168438; 218442</t>
+          <t>167404; 214266</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136627; 177677</t>
+          <t>134600; 177712</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113518; 525836</t>
+          <t>66786; 101363</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59367; 89983</t>
+          <t>58645; 89737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44604; 70648</t>
+          <t>45017; 70587</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18772; 36030</t>
+          <t>19763; 38532</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>235921; 290811</t>
+          <t>236763; 291506</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>188216; 238732</t>
+          <t>191571; 242773</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>136674; 646768</t>
+          <t>92469; 131819</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154102</t>
+          <t>175444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>136046</t>
+          <t>150069</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>290148</t>
+          <t>325513</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>250510; 307822</t>
+          <t>246982; 306719</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>295572; 355455</t>
+          <t>293124; 356100</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>132231; 183173</t>
+          <t>149251; 206282</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>196871; 249025</t>
+          <t>196324; 247708</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>229538; 285031</t>
+          <t>229784; 283995</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63620; 179470</t>
+          <t>131680; 171366</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>459543; 539953</t>
+          <t>460740; 539168</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>543494; 625971</t>
+          <t>540129; 623433</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>203054; 336576</t>
+          <t>292451; 358803</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94375</t>
+          <t>101183</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>158138</t>
+          <t>169575</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80119; 116755</t>
+          <t>79426; 115104</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103082; 143777</t>
+          <t>102797; 142586</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49032; 83646</t>
+          <t>50977; 89197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163647; 210234</t>
+          <t>163188; 212536</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>134709; 180409</t>
+          <t>134592; 179999</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69627; 115978</t>
+          <t>85461; 118330</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>249090; 312345</t>
+          <t>253696; 312496</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>249461; 308868</t>
+          <t>250834; 312010</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>127592; 183366</t>
+          <t>145765; 194959</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97288</t>
+          <t>103568</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>139305</t>
+          <t>143512</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>81100; 113923</t>
+          <t>82619; 114590</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>74111; 105256</t>
+          <t>74332; 107405</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23736; 67911</t>
+          <t>24189; 64788</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>243000; 301882</t>
+          <t>240737; 298406</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>300090; 361757</t>
+          <t>298791; 359970</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81075; 118732</t>
+          <t>86662; 127100</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>334381; 401047</t>
+          <t>333033; 400693</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>385446; 454363</t>
+          <t>385133; 457278</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111681; 170391</t>
+          <t>118626; 174544</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>818434</t>
+          <t>616802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>552599</t>
+          <t>601631</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1371033</t>
+          <t>1218433</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>959257; 1071189</t>
+          <t>957819; 1071722</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>918855; 1024531</t>
+          <t>915772; 1030277</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>599932; 1397069</t>
+          <t>566352; 676982</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>952920; 1061610</t>
+          <t>949511; 1055854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1035900; 1145841</t>
+          <t>1035312; 1145577</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>445836; 611692</t>
+          <t>566020; 645421</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1932517; 2098898</t>
+          <t>1941907; 2089338</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1987150; 2144320</t>
+          <t>1983208; 2140852</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1137263; 2124200</t>
+          <t>1152162; 1286289</t>
         </is>
       </c>
     </row>
